--- a/KatalonData/RADTestData/ChangePaymentMethod.xlsx
+++ b/KatalonData/RADTestData/ChangePaymentMethod.xlsx
@@ -8,19 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{15320F08-3095-4833-B9A5-DE0F3607F594}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr documentId="13_ncr:1_{8E8275FB-2B77-497E-870C-D80613C2C006}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
   <bookViews>
-    <workbookView windowHeight="15675" windowWidth="28995" xWindow="14303" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-2010"/>
+    <workbookView activeTab="5" windowHeight="15675" windowWidth="28995" xWindow="14303" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-2010"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" r:id="rId1" sheetId="1"/>
     <sheet name="Existing" r:id="rId2" sheetId="2"/>
     <sheet name="Extension" r:id="rId3" sheetId="3"/>
     <sheet name="NewTaxReturn" r:id="rId4" sheetId="4"/>
-    <sheet name="Personal" r:id="rId5" sheetId="5"/>
-    <sheet name="Personal_IND" r:id="rId6" sheetId="6"/>
-    <sheet name="Personal_JNT" r:id="rId7" sheetId="7"/>
-    <sheet name="Personal_EL" r:id="rId8" sheetId="8"/>
+    <sheet name="Personal_IND" r:id="rId5" sheetId="6"/>
+    <sheet name="Personal_JNT" r:id="rId6" sheetId="7"/>
+    <sheet name="Personal_EL" r:id="rId7" sheetId="8"/>
   </sheets>
   <definedNames>
     <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">NewTaxReturn!$E$1:$E$61</definedName>
@@ -46,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="975" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="162">
   <si>
     <t>Result</t>
   </si>
@@ -90,9 +89,6 @@
     <t>PTE Tax Electing S Corp</t>
   </si>
   <si>
-    <t>Existing Liability w/Notice Number</t>
-  </si>
-  <si>
     <t>Extension Payments</t>
   </si>
   <si>
@@ -141,9 +137,6 @@
     <t>2022</t>
   </si>
   <si>
-    <t>2021</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
@@ -399,235 +392,145 @@
     <t>This is in QA and Demo but not in Production</t>
   </si>
   <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:24:17 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:24:48 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:25:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:27:11 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:27:41 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:28:12 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:28:40 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:29:09 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:29:37 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:30:07 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:30:39 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:31:08 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:31:36 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:32:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:32:35 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:33:04 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:33:33 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:34:02 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:34:31 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:35:01 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:35:30 EST 2025</t>
+  </si>
+  <si>
+    <t>Mon Nov 10 10:35:59 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 14:46:12 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 14:46:47 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 14:47:20 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 15:42:04 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 15:42:34 EST 2025</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 15:43:21 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 15:44:46 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 15:45:44 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 15:47:13 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 16:18:26 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 16:18:56 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 16:28:42 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 16:52:36 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 16:53:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 16:53:34 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 16:54:03 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 16:54:31 EST 2025</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 14:58:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 14:58:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 14:59:29 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:00:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:00:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:01:00 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:04:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:04:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:05:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:05:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:06:15 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:06:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:59:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 15:59:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:00:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:00:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:01:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:01:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:04:58 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:05:32 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:06:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:06:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:07:06 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:07:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:09:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:10:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:10:57 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:11:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:12:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 16:12:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:51:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:51:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:52:25 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:52:55 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:53:24 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:53:52 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:54:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:54:49 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:55:18 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:55:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:56:14 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:56:43 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:57:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:57:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:58:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:58:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:59:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 18:59:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Fri Nov 07 19:00:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:22:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:23:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:23:45 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:24:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:24:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:25:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:27:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:27:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:28:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:28:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:29:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:29:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:30:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:30:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:31:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:31:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:32:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:32:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:33:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:33:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:34:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:34:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:35:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:35:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:35:59 EST 2025</t>
+    <t>Tue Nov 25 18:41:27 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 18:42:05 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 18:42:38 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 18:43:10 EST 2025</t>
+  </si>
+  <si>
+    <t>Tue Nov 25 18:43:44 EST 2025</t>
   </si>
 </sst>
 </file>
@@ -1043,24 +946,24 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -1069,27 +972,27 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>170</v>
+        <v>139</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -1098,27 +1001,27 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>48</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>171</v>
+        <v>140</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -1127,30 +1030,30 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -1159,30 +1062,30 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -1191,30 +1094,30 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
         <v>118</v>
       </c>
-      <c r="B7" t="s">
-        <v>174</v>
-      </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
@@ -1223,19 +1126,19 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1282,478 +1185,478 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B2" t="s">
-        <v>175</v>
+        <v>119</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B3" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B4" t="s">
-        <v>177</v>
+        <v>121</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B5" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B6" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B8" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B9" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B10" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B11" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B12" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B13" t="s">
-        <v>186</v>
+        <v>130</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I13" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B14" t="s">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B15" t="s">
-        <v>188</v>
+        <v>132</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="I15" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B16" t="s">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I16" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B17" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B18" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E20" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="J20" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="J20" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="B21" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
   </sheetData>
@@ -1803,139 +1706,163 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+      <c r="A2" t="s">
+        <v>143</v>
+      </c>
+      <c r="B2" t="s">
+        <v>147</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>141</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>142</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+      <c r="A5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" t="s">
+        <v>144</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>145</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+      <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>146</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -1984,32 +1911,36 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>148</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>9</v>
@@ -2018,17 +1949,21 @@
         <v>2024</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>149</v>
+      </c>
       <c r="C3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>10</v>
@@ -2037,20 +1972,20 @@
         <v>2024</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A4"/>
       <c r="B4"/>
       <c r="C4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>11</v>
@@ -2059,20 +1994,20 @@
         <v>2024</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A5"/>
       <c r="B5"/>
       <c r="C5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>12</v>
@@ -2081,20 +2016,20 @@
         <v>2024</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A6"/>
       <c r="B6"/>
       <c r="C6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>13</v>
@@ -2103,20 +2038,20 @@
         <v>2024</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>9</v>
@@ -2125,17 +2060,17 @@
         <v>2023</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>10</v>
@@ -2144,20 +2079,20 @@
         <v>2023</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>11</v>
@@ -2166,20 +2101,20 @@
         <v>2023</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A10"/>
       <c r="B10"/>
       <c r="C10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>12</v>
@@ -2188,20 +2123,20 @@
         <v>2023</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A11"/>
       <c r="B11"/>
       <c r="C11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>13</v>
@@ -2210,20 +2145,20 @@
         <v>2023</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A12"/>
       <c r="B12"/>
       <c r="C12" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>9</v>
@@ -2232,17 +2167,17 @@
         <v>2022</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A13"/>
       <c r="B13"/>
       <c r="C13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>10</v>
@@ -2251,20 +2186,20 @@
         <v>2022</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A14"/>
       <c r="B14"/>
       <c r="C14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>11</v>
@@ -2273,20 +2208,20 @@
         <v>2022</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A15"/>
       <c r="B15"/>
       <c r="C15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>12</v>
@@ -2295,20 +2230,20 @@
         <v>2022</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A16"/>
       <c r="B16"/>
       <c r="C16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E16" s="1" t="s">
         <v>13</v>
@@ -2317,95 +2252,95 @@
         <v>2022</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K16" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A17"/>
       <c r="B17"/>
       <c r="C17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F17" s="1">
         <v>2025</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K17" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A18"/>
       <c r="B18"/>
       <c r="C18" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F18" s="1">
         <v>2025</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F19" s="1">
         <v>2025</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A20"/>
       <c r="B20"/>
       <c r="C20" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E20" s="1" t="s">
         <v>8</v>
@@ -2414,295 +2349,295 @@
         <v>2024</v>
       </c>
       <c r="K20" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A21"/>
       <c r="B21"/>
       <c r="C21" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F21" s="1">
         <v>2025</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K21" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A22"/>
       <c r="B22"/>
       <c r="C22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F22" s="1">
         <v>2025</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I22" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K22" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A23"/>
       <c r="B23"/>
       <c r="C23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F23" s="1">
         <v>2025</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K23" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A24"/>
       <c r="B24"/>
       <c r="C24" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F24" s="1">
         <v>2025</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I24" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K24" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A25"/>
       <c r="B25"/>
       <c r="C25" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F25" s="1">
         <v>2025</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I25" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K25" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A26"/>
       <c r="B26"/>
       <c r="C26" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F26" s="1">
         <v>2025</v>
       </c>
       <c r="H26" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K26" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A27"/>
       <c r="B27"/>
       <c r="C27" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F27" s="1">
         <v>2025</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K27" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A28"/>
       <c r="B28"/>
       <c r="C28" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F28" s="1">
         <v>2025</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I28" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A29"/>
       <c r="B29"/>
       <c r="C29" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F29" s="1">
         <v>2024</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A30"/>
       <c r="B30"/>
       <c r="C30" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I30" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A31"/>
       <c r="B31"/>
       <c r="C31" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F31" s="1">
         <v>2024</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A32"/>
       <c r="B32"/>
       <c r="C32" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
@@ -2711,295 +2646,295 @@
         <v>2023</v>
       </c>
       <c r="K32" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A33"/>
       <c r="B33"/>
       <c r="C33" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E33" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F33" s="1">
         <v>2024</v>
       </c>
       <c r="I33" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K33" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A34"/>
       <c r="B34"/>
       <c r="C34" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E34" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F34" s="1">
         <v>2024</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I34" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K34" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A35"/>
       <c r="B35"/>
       <c r="C35" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F35" s="1">
         <v>2024</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K35" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A36"/>
       <c r="B36"/>
       <c r="C36" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F36" s="1">
         <v>2024</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K36" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A37"/>
       <c r="B37"/>
       <c r="C37" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E37" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F37" s="1">
         <v>2024</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H37" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I37" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K37" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A38"/>
       <c r="B38"/>
       <c r="C38" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E38" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F38" s="1">
         <v>2024</v>
       </c>
       <c r="H38" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I38" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K38" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A39"/>
       <c r="B39"/>
       <c r="C39" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E39" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F39" s="1">
         <v>2024</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K39" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A40"/>
       <c r="B40"/>
       <c r="C40" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E40" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F40" s="1">
         <v>2024</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I40" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A41"/>
       <c r="B41"/>
       <c r="C41" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F41" s="1">
         <v>2023</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A42"/>
       <c r="B42"/>
       <c r="C42" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E42" s="1" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F42" s="1">
         <v>2023</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I42" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A43"/>
       <c r="B43"/>
       <c r="C43" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F43" s="1">
         <v>2023</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I43" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A44"/>
       <c r="B44"/>
       <c r="C44" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E44" s="1" t="s">
         <v>8</v>
@@ -3008,399 +2943,399 @@
         <v>2022</v>
       </c>
       <c r="K44" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A45"/>
       <c r="B45"/>
       <c r="C45" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E45" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F45" s="1">
         <v>2023</v>
       </c>
       <c r="I45" s="1" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="J45" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K45" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A46"/>
       <c r="B46"/>
       <c r="C46" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D46" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E46" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F46" s="1">
         <v>2023</v>
       </c>
       <c r="H46" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I46" s="1" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="K46" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A47"/>
       <c r="B47"/>
       <c r="C47" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D47" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E47" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F47" s="1">
         <v>2023</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K47" s="1" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A48"/>
       <c r="B48"/>
       <c r="C48" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D48" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F48" s="1">
         <v>2023</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I48" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="K48" s="1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A49"/>
       <c r="B49"/>
       <c r="C49" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F49" s="1">
         <v>2023</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="K49" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A50"/>
       <c r="B50"/>
       <c r="C50" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F50" s="1">
         <v>2023</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="K50" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A51"/>
       <c r="B51"/>
       <c r="C51" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F51" s="1">
         <v>2023</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="K51" s="1" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A52"/>
       <c r="B52"/>
       <c r="C52" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F52" s="1">
         <v>2023</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A53"/>
       <c r="B53"/>
       <c r="C53" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E53" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A54"/>
       <c r="B54"/>
       <c r="C54" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A56"/>
       <c r="B56"/>
       <c r="C56" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F56" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="L56" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="F56" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="L56" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A57"/>
       <c r="B57"/>
       <c r="C57" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A59"/>
       <c r="B59"/>
       <c r="C59" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E59" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="F59" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="L59" s="1" t="s">
         <v>114</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="L59" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A60"/>
       <c r="B60"/>
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.35">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D61" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>
@@ -3414,128 +3349,6 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C48EC9F-E6C0-40A2-877C-8FE515BAA791}">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="22.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="26.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C2" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C4" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="C7" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <headerFooter>
-    <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
   <dimension ref="A1:I9"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3570,153 +3383,173 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>151</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>153</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
-      <c r="C4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>155</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
@@ -3724,7 +3557,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3759,102 +3592,122 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>157</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>115</v>
+      </c>
+      <c r="B5" t="s">
+        <v>160</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3"/>
-      <c r="B3"/>
-      <c r="C3" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
-      <c r="C4" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="1" t="s">
+      <c r="G5" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B6" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G4" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
-      <c r="C5" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
-      <c r="C6" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -3862,7 +3715,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
   <dimension ref="A1:G3"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -3892,36 +3745,40 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A2"/>
-      <c r="B2"/>
+      <c r="A2" t="s">
+        <v>115</v>
+      </c>
+      <c r="B2" t="s">
+        <v>150</v>
+      </c>
       <c r="C2" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/KatalonData/RADTestData/ChangePaymentMethod.xlsx
+++ b/KatalonData/RADTestData/ChangePaymentMethod.xlsx
@@ -1,32 +1,32 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{8E8275FB-2B77-497E-870C-D80613C2C006}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59179EE5-507F-4142-87F4-8AD6114AECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="5" windowHeight="15675" windowWidth="28995" xWindow="14303" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}" yWindow="-2010"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Estimated" r:id="rId1" sheetId="1"/>
-    <sheet name="Existing" r:id="rId2" sheetId="2"/>
-    <sheet name="Extension" r:id="rId3" sheetId="3"/>
-    <sheet name="NewTaxReturn" r:id="rId4" sheetId="4"/>
-    <sheet name="Personal_IND" r:id="rId5" sheetId="6"/>
-    <sheet name="Personal_JNT" r:id="rId6" sheetId="7"/>
-    <sheet name="Personal_EL" r:id="rId7" sheetId="8"/>
+    <sheet name="Estimated" sheetId="1" r:id="rId1"/>
+    <sheet name="Existing" sheetId="2" r:id="rId2"/>
+    <sheet name="Extension" sheetId="3" r:id="rId3"/>
+    <sheet name="NewTaxReturn" sheetId="4" r:id="rId4"/>
+    <sheet name="Personal_IND" sheetId="6" r:id="rId5"/>
+    <sheet name="Personal_JNT" sheetId="7" r:id="rId6"/>
+    <sheet name="Personal_EL" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="3" name="_xlnm._FilterDatabase">NewTaxReturn!$E$1:$E$61</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">NewTaxReturn!$E$1:$E$61</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="748" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="216">
   <si>
     <t>Result</t>
   </si>
@@ -134,9 +134,6 @@
     <t>Alcohol Tax</t>
   </si>
   <si>
-    <t>2022</t>
-  </si>
-  <si>
     <t>Y</t>
   </si>
   <si>
@@ -395,149 +392,313 @@
     <t>Pass</t>
   </si>
   <si>
-    <t>Mon Nov 10 10:24:17 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:24:48 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:25:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:27:11 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:27:41 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:28:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:28:40 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:29:09 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:29:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:30:07 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:30:39 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:31:08 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:31:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:32:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:32:35 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:33:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:33:33 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:34:02 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:34:31 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:35:01 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:35:30 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Nov 10 10:35:59 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 14:46:12 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 14:46:47 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 14:47:20 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 15:42:04 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 15:42:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 15:43:21 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 15:44:46 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 15:45:44 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 15:47:13 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 16:18:26 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 16:18:56 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 16:28:42 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 16:52:36 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 16:53:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 16:53:34 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 16:54:03 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 16:54:31 EST 2025</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Tue Nov 25 18:41:27 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 18:42:05 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 18:42:38 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 18:43:10 EST 2025</t>
-  </si>
-  <si>
-    <t>Tue Nov 25 18:43:44 EST 2025</t>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:32:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:33:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:34:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:35:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:36:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:37:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:38:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:54:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:55:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:56:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:57:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:57:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:58:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 22:59:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:00:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:01:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:01:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:02:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:03:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:04:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:05:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:06:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:06:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:07:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:08:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:09:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:10:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:11:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:12:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:13:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:14:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat May 23 23:16:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:42:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:44:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:45:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:46:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:48:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:49:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:50:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:52:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:54:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:55:40 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun May 24 04:57:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:41:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:41:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:42:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:42:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:43:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:43:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:44:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:44:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:44:58 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:45:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:45:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:46:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:46:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:47:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:47:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:47:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:48:16 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:48:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:49:04 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:49:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:49:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:50:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:50:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:51:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:51:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:51:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:52:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:52:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:53:07 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:53:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:53:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:54:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:54:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:55:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:55:33 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:56:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:56:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:56:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:57:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:57:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:58:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:58:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:59:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:59:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 15:59:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:00:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:00:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:01:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:01:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:02:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:02:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:02:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:03:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:03:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:04:12 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:04:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Mon May 25 16:05:01 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -586,19 +747,19 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -615,10 +776,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -653,7 +814,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -705,7 +866,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -816,21 +977,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -847,7 +1008,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -899,31 +1060,31 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
-  <dimension ref="A1:K7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19BDCA51-7A9D-4BB2-A660-F3BEEC814D67}">
+  <dimension ref="A1:J8"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.1796875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.54296875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.54296875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.54296875" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.26953125" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.26953125" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.54296875" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.1796875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="18.453125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -946,24 +1107,24 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>138</v>
+        <v>116</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -972,27 +1133,27 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>18</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>117</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>7</v>
@@ -1001,27 +1162,27 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>118</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>7</v>
@@ -1030,30 +1191,30 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G4" s="1" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>7</v>
@@ -1062,30 +1223,30 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>21</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>7</v>
@@ -1094,30 +1255,30 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G6" s="1" t="s">
         <v>22</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>7</v>
@@ -1126,25 +1287,48 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G7" s="1" t="s">
         <v>23</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>98</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1152,23 +1336,23 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FAB49CF7-E4D4-4F06-BD88-EA9191F7BC6F}">
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.54296875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.26953125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.6328125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.453125" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.1796875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.1796875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="43.36328125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1185,482 +1369,482 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>8</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>9</v>
       </c>
       <c r="I4" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>10</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>11</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B8" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>26</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B9" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B10" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>28</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B11" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B12" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>13</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="G13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I13" s="1" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>115</v>
-      </c>
-      <c r="B13" t="s">
-        <v>130</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="1" t="s">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>135</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="H14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I14" s="1" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" t="s">
-        <v>115</v>
-      </c>
-      <c r="B14" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E14" s="1" t="s">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" t="s">
+        <v>136</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E15" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="H14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I14" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B15" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E15" s="1" t="s">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="F16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I16" s="1" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" t="s">
-        <v>133</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E16" s="1" t="s">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E17" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="1" t="s">
+      <c r="G17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="1" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>115</v>
-      </c>
-      <c r="B17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E17" s="1" t="s">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" t="s">
+        <v>139</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="E18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="G17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1" t="s">
+      <c r="F18" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I18" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>115</v>
-      </c>
-      <c r="B18" t="s">
-        <v>135</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="E18" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A19"/>
       <c r="B19"/>
       <c r="C19" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B20" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B21" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1668,22 +1852,22 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
-  <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A22222EF-2A37-441E-9CE4-90FD36DC8DDC}">
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.26953125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.453125" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1706,21 +1890,21 @@
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>14</v>
@@ -1729,24 +1913,24 @@
         <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>21</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -1755,21 +1939,21 @@
         <v>9</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>14</v>
@@ -1778,24 +1962,24 @@
         <v>10</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>143</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>14</v>
@@ -1804,24 +1988,24 @@
         <v>11</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>14</v>
@@ -1830,24 +2014,24 @@
         <v>12</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B7" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>14</v>
@@ -1856,18 +2040,18 @@
         <v>13</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -1875,23 +2059,23 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:M61"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
+  <dimension ref="A1:L61"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.1796875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.7265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.7265625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="41.26953125" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
-    <col min="7" max="10" customWidth="true" style="1" width="19.81640625" collapsed="true"/>
-    <col min="11" max="11" style="1" width="9.1796875" collapsed="true"/>
-    <col min="12" max="12" customWidth="true" style="1" width="43.1796875" collapsed="true"/>
-    <col min="13" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="9.19921875" style="1" collapsed="1"/>
+    <col min="12" max="12" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1911,33 +2095,33 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>6</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>15</v>
@@ -1945,22 +2129,22 @@
       <c r="E2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="1">
-        <v>2024</v>
+      <c r="F2" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>149</v>
+        <v>160</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>15</v>
@@ -1968,21 +2152,25 @@
       <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="1">
-        <v>2024</v>
+      <c r="F3" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4"/>
-      <c r="B4"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" t="s">
+        <v>161</v>
+      </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -1990,21 +2178,25 @@
       <c r="E4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="1">
-        <v>2024</v>
+      <c r="F4" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A5"/>
-      <c r="B5"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" t="s">
+        <v>162</v>
+      </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -2012,21 +2204,25 @@
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F5" s="1">
-        <v>2024</v>
+      <c r="F5" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K5" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6"/>
-      <c r="B6"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" t="s">
+        <v>163</v>
+      </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -2034,21 +2230,25 @@
       <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="1">
-        <v>2024</v>
+      <c r="F6" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K6" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A7"/>
-      <c r="B7"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" t="s">
+        <v>164</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -2056,18 +2256,22 @@
       <c r="E7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F7" s="1">
-        <v>2023</v>
+      <c r="F7" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="K7" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8"/>
-      <c r="B8"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" t="s">
+        <v>165</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>15</v>
@@ -2075,21 +2279,25 @@
       <c r="E8" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F8" s="1">
-        <v>2023</v>
+      <c r="F8" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K8" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A9"/>
-      <c r="B9"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>166</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
@@ -2097,21 +2305,25 @@
       <c r="E9" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="1">
-        <v>2023</v>
+      <c r="F9" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K9" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10"/>
-      <c r="B10"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A10" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" t="s">
+        <v>167</v>
+      </c>
       <c r="C10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>15</v>
@@ -2119,21 +2331,25 @@
       <c r="E10" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F10" s="1">
-        <v>2023</v>
+      <c r="F10" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K10" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A11"/>
-      <c r="B11"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" t="s">
+        <v>168</v>
+      </c>
       <c r="C11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>15</v>
@@ -2141,21 +2357,25 @@
       <c r="E11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F11" s="1">
-        <v>2023</v>
+      <c r="F11" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12"/>
-      <c r="B12"/>
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A12" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" t="s">
+        <v>169</v>
+      </c>
       <c r="C12" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>15</v>
@@ -2163,18 +2383,22 @@
       <c r="E12" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="1">
-        <v>2022</v>
+      <c r="F12" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A13"/>
-      <c r="B13"/>
+        <v>72</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A13" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" t="s">
+        <v>170</v>
+      </c>
       <c r="C13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>15</v>
@@ -2182,21 +2406,25 @@
       <c r="E13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="F13" s="1">
-        <v>2022</v>
+      <c r="F13" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K13" s="1" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14"/>
-      <c r="B14"/>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A14" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" t="s">
+        <v>171</v>
+      </c>
       <c r="C14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>15</v>
@@ -2204,21 +2432,25 @@
       <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F14" s="1">
-        <v>2022</v>
+      <c r="F14" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K14" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A15"/>
-      <c r="B15"/>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A15" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" t="s">
+        <v>172</v>
+      </c>
       <c r="C15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>15</v>
@@ -2226,21 +2458,25 @@
       <c r="E15" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F15" s="1">
-        <v>2022</v>
+      <c r="F15" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K15" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16"/>
-      <c r="B16"/>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A16" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" t="s">
+        <v>173</v>
+      </c>
       <c r="C16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>15</v>
@@ -2248,46 +2484,54 @@
       <c r="E16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F16" s="1">
-        <v>2022</v>
+      <c r="F16" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K16" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
+        <v>174</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="K17" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A17"/>
-      <c r="B17"/>
-      <c r="C17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F17" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18"/>
-      <c r="B18"/>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A18" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" t="s">
+        <v>175</v>
+      </c>
       <c r="C18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>15</v>
@@ -2295,24 +2539,28 @@
       <c r="E18" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F18" s="1">
-        <v>2025</v>
+      <c r="F18" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I18" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K18" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A19"/>
-      <c r="B19"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A19" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" t="s">
+        <v>176</v>
+      </c>
       <c r="C19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>15</v>
@@ -2320,24 +2568,28 @@
       <c r="E19" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F19" s="1">
-        <v>2025</v>
+      <c r="F19" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I19" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K19" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20"/>
-      <c r="B20"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A20" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" t="s">
+        <v>177</v>
+      </c>
       <c r="C20" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>15</v>
@@ -2345,90 +2597,106 @@
       <c r="E20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1">
-        <v>2024</v>
+      <c r="F20" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="K20" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A21" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" t="s">
+        <v>178</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I21" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J21" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K21" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A21"/>
-      <c r="B21"/>
-      <c r="C21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="1" t="s">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A22" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" t="s">
+        <v>179</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F22" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H22" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I22" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K22" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A23" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" t="s">
+        <v>180</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F21" s="1">
-        <v>2025</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J21" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22"/>
-      <c r="B22"/>
-      <c r="C22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E22" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F22" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="F23" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K23" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A23"/>
-      <c r="B23"/>
-      <c r="C23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F23" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24"/>
-      <c r="B24"/>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A24" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" t="s">
+        <v>181</v>
+      </c>
       <c r="C24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>15</v>
@@ -2436,102 +2704,118 @@
       <c r="E24" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F24" s="1">
-        <v>2025</v>
+      <c r="F24" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="H24" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I24" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K24" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A25" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" t="s">
+        <v>182</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H25" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="K25" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A25"/>
-      <c r="B25"/>
-      <c r="C25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="1" t="s">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A26" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" t="s">
+        <v>183</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F25" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I25" s="1" t="s">
+      <c r="F26" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="K26" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26"/>
-      <c r="B26"/>
-      <c r="C26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="1" t="s">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A27" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" t="s">
+        <v>184</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D27" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F26" s="1">
-        <v>2025</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="F27" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="G27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H27" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K27" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A27"/>
-      <c r="B27"/>
-      <c r="C27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F27" s="1">
-        <v>2025</v>
-      </c>
-      <c r="G27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28"/>
-      <c r="B28"/>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A28" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" t="s">
+        <v>185</v>
+      </c>
       <c r="C28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>15</v>
@@ -2539,52 +2823,60 @@
       <c r="E28" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F28" s="1">
-        <v>2025</v>
+      <c r="F28" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K28" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A29"/>
-      <c r="B29"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A29" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" t="s">
+        <v>186</v>
+      </c>
       <c r="C29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F29" s="1">
-        <v>2024</v>
+        <v>34</v>
+      </c>
+      <c r="F29" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30"/>
-      <c r="B30"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A30" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" t="s">
+        <v>187</v>
+      </c>
       <c r="C30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>15</v>
@@ -2593,23 +2885,27 @@
         <v>28</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I30" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K30" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A31"/>
-      <c r="B31"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A31" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" t="s">
+        <v>188</v>
+      </c>
       <c r="C31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>15</v>
@@ -2617,24 +2913,28 @@
       <c r="E31" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F31" s="1">
-        <v>2024</v>
+      <c r="F31" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I31" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K31" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32"/>
-      <c r="B32"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" t="s">
+        <v>189</v>
+      </c>
       <c r="C32" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>15</v>
@@ -2642,90 +2942,106 @@
       <c r="E32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="1">
-        <v>2023</v>
+      <c r="F32" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="K32" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A33" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" t="s">
+        <v>190</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F33" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I33" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J33" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K33" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A33"/>
-      <c r="B33"/>
-      <c r="C33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="1" t="s">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A34" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H34" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I34" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A35" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" t="s">
+        <v>192</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D35" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E35" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F33" s="1">
-        <v>2024</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J33" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34"/>
-      <c r="B34"/>
-      <c r="C34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E34" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F34" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K34" s="1" t="s">
+      <c r="F35" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H35" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K35" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A35"/>
-      <c r="B35"/>
-      <c r="C35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E35" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F35" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36"/>
-      <c r="B36"/>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A36" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" t="s">
+        <v>193</v>
+      </c>
       <c r="C36" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D36" s="1" t="s">
         <v>15</v>
@@ -2733,102 +3049,118 @@
       <c r="E36" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F36" s="1">
-        <v>2024</v>
+      <c r="F36" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I36" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K36" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A37" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D37" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E37" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F37" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I37" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="K37" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A37"/>
-      <c r="B37"/>
-      <c r="C37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E37" s="1" t="s">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A38" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" t="s">
+        <v>195</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D38" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E38" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F37" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H37" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I37" s="1" t="s">
+      <c r="F38" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="H38" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="K38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38"/>
-      <c r="B38"/>
-      <c r="C38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E38" s="1" t="s">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A39" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" t="s">
+        <v>196</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E39" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F38" s="1">
-        <v>2024</v>
-      </c>
-      <c r="H38" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I38" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K38" s="1" t="s">
+      <c r="F39" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H39" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K39" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A39"/>
-      <c r="B39"/>
-      <c r="C39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E39" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F39" s="1">
-        <v>2024</v>
-      </c>
-      <c r="G39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H39" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40"/>
-      <c r="B40"/>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A40" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" t="s">
+        <v>197</v>
+      </c>
       <c r="C40" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D40" s="1" t="s">
         <v>15</v>
@@ -2836,52 +3168,60 @@
       <c r="E40" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F40" s="1">
-        <v>2024</v>
+      <c r="F40" s="1" t="s">
+        <v>109</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I40" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K40" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L40" s="1" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A41"/>
-      <c r="B41"/>
+        <v>112</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A41" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" t="s">
+        <v>198</v>
+      </c>
       <c r="C41" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D41" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E41" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="F41" s="1">
-        <v>2023</v>
+        <v>34</v>
+      </c>
+      <c r="F41" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I41" s="1" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K41" s="1" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42"/>
-      <c r="B42"/>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A42" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" t="s">
+        <v>199</v>
+      </c>
       <c r="C42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D42" s="1" t="s">
         <v>15</v>
@@ -2889,24 +3229,28 @@
       <c r="E42" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="F42" s="1">
-        <v>2023</v>
+      <c r="F42" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I42" s="1" t="s">
         <v>22</v>
       </c>
       <c r="K42" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A43"/>
-      <c r="B43"/>
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A43" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" t="s">
+        <v>200</v>
+      </c>
       <c r="C43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D43" s="1" t="s">
         <v>15</v>
@@ -2914,24 +3258,28 @@
       <c r="E43" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="F43" s="1">
-        <v>2023</v>
+      <c r="F43" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I43" s="1" t="s">
         <v>18</v>
       </c>
       <c r="K43" s="1" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44"/>
-      <c r="B44"/>
+        <v>79</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A44" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" t="s">
+        <v>201</v>
+      </c>
       <c r="C44" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D44" s="1" t="s">
         <v>15</v>
@@ -2939,90 +3287,106 @@
       <c r="E44" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F44" s="1">
-        <v>2022</v>
+      <c r="F44" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="K44" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A45" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E45" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F45" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I45" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="J45" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K45" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A45"/>
-      <c r="B45"/>
-      <c r="C45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E45" s="1" t="s">
+    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A46" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" t="s">
+        <v>203</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E46" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F46" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H46" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="K46" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A47" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" t="s">
+        <v>204</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D47" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="F45" s="1">
-        <v>2023</v>
-      </c>
-      <c r="I45" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J45" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46"/>
-      <c r="B46"/>
-      <c r="C46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E46" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F46" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H46" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I46" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K46" s="1" t="s">
+      <c r="F47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H47" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K47" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A47"/>
-      <c r="B47"/>
-      <c r="C47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E47" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="F47" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H47" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48"/>
-      <c r="B48"/>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A48" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" t="s">
+        <v>205</v>
+      </c>
       <c r="C48" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D48" s="1" t="s">
         <v>15</v>
@@ -3030,102 +3394,118 @@
       <c r="E48" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="F48" s="1">
-        <v>2023</v>
+      <c r="F48" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I48" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K48" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A49" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" t="s">
+        <v>206</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="F49" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H49" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="K49" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A49"/>
-      <c r="B49"/>
-      <c r="C49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E49" s="1" t="s">
+    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A50" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" t="s">
+        <v>207</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D50" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E50" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="F49" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H49" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I49" s="1" t="s">
+      <c r="F50" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="H50" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="K50" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50"/>
-      <c r="B50"/>
-      <c r="C50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E50" s="1" t="s">
+    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A51" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" t="s">
+        <v>208</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D51" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E51" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="F50" s="1">
-        <v>2023</v>
-      </c>
-      <c r="H50" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I50" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="K50" s="1" t="s">
+      <c r="F51" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A51"/>
-      <c r="B51"/>
-      <c r="C51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E51" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="F51" s="1">
-        <v>2023</v>
-      </c>
-      <c r="G51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="H51" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52"/>
-      <c r="B52"/>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A52" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" t="s">
+        <v>209</v>
+      </c>
       <c r="C52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D52" s="1" t="s">
         <v>15</v>
@@ -3133,215 +3513,239 @@
       <c r="E52" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="F52" s="1">
-        <v>2023</v>
+      <c r="F52" s="1" t="s">
+        <v>33</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I52" s="1" t="s">
         <v>19</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="L52" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A53" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" t="s">
+        <v>210</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F53" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A53"/>
-      <c r="B53"/>
-      <c r="C53" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E53" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F53" s="1" t="s">
+    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A54" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" t="s">
+        <v>211</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D54" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E54" s="1" t="s">
         <v>110</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54"/>
-      <c r="B54"/>
-      <c r="C54" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E54" s="1" t="s">
-        <v>111</v>
-      </c>
       <c r="F54" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L54" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A55"/>
       <c r="B55"/>
       <c r="C55" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D55" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I55" s="1" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56"/>
-      <c r="B56"/>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A56" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" t="s">
+        <v>212</v>
+      </c>
       <c r="C56" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D56" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="L56" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A57"/>
-      <c r="B57"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A57" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" t="s">
+        <v>213</v>
+      </c>
       <c r="C57" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L57" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A58"/>
       <c r="B58"/>
       <c r="C58" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D58" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E58" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F58" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="G58" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A59" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" t="s">
+        <v>214</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="F59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D58" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E58" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F58" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G58" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="I58" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A59"/>
-      <c r="B59"/>
-      <c r="C59" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E59" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="F59" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="L59" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60"/>
-      <c r="B60"/>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
+      <c r="A60" t="s">
+        <v>114</v>
+      </c>
+      <c r="B60" t="s">
+        <v>215</v>
+      </c>
       <c r="C60" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="L60" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A61"/>
       <c r="B61"/>
       <c r="C61" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="F61" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D61" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E61" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F61" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="G61" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="I61" s="1" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="E1:E61" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}"/>
   <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
@@ -3349,21 +3753,21 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
-  <dimension ref="A1:I9"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE13C096-3F8A-4B4D-A3EE-3415763F7F13}">
+  <dimension ref="A1:H9"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.54296875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.1796875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.1796875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="23.453125" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3383,21 +3787,21 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -3406,21 +3810,21 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -3429,21 +3833,21 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -3452,21 +3856,21 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -3475,21 +3879,21 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -3498,81 +3902,81 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7"/>
       <c r="B7"/>
       <c r="C7" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8"/>
       <c r="B8"/>
       <c r="C8" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9"/>
       <c r="B9"/>
       <c r="C9" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
-  <dimension ref="A1:H6"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A156AB6-80FF-4E48-B399-7CA373BDFD42}">
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.26953125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.1796875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="14.1796875" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3592,18 +3996,18 @@
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>7</v>
@@ -3612,21 +4016,21 @@
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>14</v>
@@ -3635,21 +4039,21 @@
         <v>16</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>15</v>
@@ -3658,21 +4062,21 @@
         <v>16</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>34</v>
+        <v>109</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>15</v>
@@ -3681,21 +4085,21 @@
         <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>15</v>
@@ -3704,31 +4108,31 @@
         <v>16</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
-  <dimension ref="A1:G3"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03F3D31C-4F04-42F4-8C54-828F1948951D}">
+  <dimension ref="A1:F3"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.1796875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.7265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.26953125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3745,43 +4149,43 @@
         <v>4</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3"/>
       <c r="B3"/>
       <c r="C3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/KatalonData/RADTestData/ChangePaymentMethod.xlsx
+++ b/KatalonData/RADTestData/ChangePaymentMethod.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59179EE5-507F-4142-87F4-8AD6114AECA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1A9B65-B8E4-413D-A306-37F2DD2B058C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="905" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="316">
   <si>
     <t>Result</t>
   </si>
@@ -470,9 +470,6 @@
     <t>Sat May 23 23:08:32 EDT 2026</t>
   </si>
   <si>
-    <t>Sat May 23 23:09:21 EDT 2026</t>
-  </si>
-  <si>
     <t>Sat May 23 23:10:07 EDT 2026</t>
   </si>
   <si>
@@ -653,9 +650,6 @@
     <t>Mon May 25 15:59:09 EDT 2026</t>
   </si>
   <si>
-    <t>Mon May 25 15:59:35 EDT 2026</t>
-  </si>
-  <si>
     <t>Mon May 25 15:59:59 EDT 2026</t>
   </si>
   <si>
@@ -680,25 +674,332 @@
     <t>Mon May 25 16:02:59 EDT 2026</t>
   </si>
   <si>
-    <t>Mon May 25 16:03:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:03:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:04:12 EDT 2026</t>
-  </si>
-  <si>
     <t>Mon May 25 16:04:37 EDT 2026</t>
   </si>
   <si>
-    <t>Mon May 25 16:05:01 EDT 2026</t>
+    <t>MFInsNum</t>
+  </si>
+  <si>
+    <t>Motor Fuel Floor Tax</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 16:05:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 16:05:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 16:06:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 16:06:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 16:06:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 22:58:30 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 22:59:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 22:59:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 22:59:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:00:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:00:45 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:01:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:01:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:02:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:02:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:02:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:03:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:03:55 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:04:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:04:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:05:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:05:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:06:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:06:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:07:22 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:07:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:08:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:08:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:09:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:09:49 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:10:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:10:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:11:13 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:11:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:12:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:12:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:13:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:13:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:13:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:14:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:14:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:15:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:15:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:15:46 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:16:09 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:16:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:16:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:17:19 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:17:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:18:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:18:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:18:50 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:19:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:19:37 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:20:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:20:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:20:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:21:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:21:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:21:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:22:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:22:43 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:23:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:23:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:23:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:24:15 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:24:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:25:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:25:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:25:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:26:10 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:26:34 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:26:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:27:20 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:27:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:28:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:28:28 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:28:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:29:14 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:29:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:30:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:30:25 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:30:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:31:11 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:31:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:31:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:32:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:32:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:33:08 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:33:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:33:54 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:34:17 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:34:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:35:03 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:35:31 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:35:59 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:36:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:36:56 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:37:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:37:52 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:38:24 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:38:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:39:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fri Jul 10 23:40:02 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1071,17 +1372,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
+    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1117,11 +1418,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" t="s">
-        <v>116</v>
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>217</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1146,11 +1447,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="s">
-        <v>117</v>
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1175,11 +1476,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="s">
-        <v>118</v>
+      <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>219</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1207,11 +1508,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>119</v>
+      <c r="A5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1239,11 +1540,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>120</v>
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>221</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1271,11 +1572,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" t="s">
-        <v>121</v>
+      <c r="A7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1303,11 +1604,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>122</v>
+      <c r="A8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>223</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1340,16 +1641,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
-    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
+    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1385,11 +1686,11 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" t="s">
-        <v>123</v>
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1408,11 +1709,11 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="s">
-        <v>124</v>
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>225</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1431,11 +1732,11 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="s">
-        <v>125</v>
+      <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>226</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1454,11 +1755,11 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>126</v>
+      <c r="A5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>227</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1480,11 +1781,11 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>127</v>
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1506,11 +1807,11 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" t="s">
-        <v>128</v>
+      <c r="A7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>229</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1529,11 +1830,11 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>129</v>
+      <c r="A8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1552,11 +1853,11 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" t="s">
-        <v>130</v>
+      <c r="A9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>231</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1575,11 +1876,11 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" t="s">
-        <v>131</v>
+      <c r="A10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1598,11 +1899,11 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" t="s">
-        <v>132</v>
+      <c r="A11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>233</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1621,11 +1922,11 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" t="s">
-        <v>133</v>
+      <c r="A12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1644,11 +1945,11 @@
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" t="s">
-        <v>134</v>
+      <c r="A13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>235</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1667,11 +1968,11 @@
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" t="s">
-        <v>135</v>
+      <c r="A14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1690,11 +1991,11 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" t="s">
-        <v>136</v>
+      <c r="A15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>237</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -1710,11 +2011,11 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" t="s">
-        <v>137</v>
+      <c r="A16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -1736,11 +2037,11 @@
       </c>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" t="s">
-        <v>138</v>
+      <c r="A17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>239</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -1759,11 +2060,11 @@
       </c>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" t="s">
-        <v>139</v>
+      <c r="A18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>240</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -1782,8 +2083,6 @@
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A19"/>
-      <c r="B19"/>
       <c r="C19" s="1" t="s">
         <v>32</v>
       </c>
@@ -1801,11 +2100,11 @@
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" t="s">
-        <v>140</v>
+      <c r="A20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>241</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -1821,14 +2120,8 @@
       </c>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>141</v>
-      </c>
       <c r="C21" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>107</v>
@@ -1856,15 +2149,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -1897,11 +2190,11 @@
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" t="s">
-        <v>142</v>
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>242</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1923,11 +2216,11 @@
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="s">
-        <v>143</v>
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>243</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1946,11 +2239,11 @@
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="s">
-        <v>144</v>
+      <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>244</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1972,11 +2265,11 @@
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>145</v>
+      <c r="A5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>245</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1998,11 +2291,11 @@
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>146</v>
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>246</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2024,11 +2317,11 @@
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" t="s">
-        <v>147</v>
+      <c r="A7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>247</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2060,22 +2353,23 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3B7105E-5E71-456F-8D2A-C4C503B29111}">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="9.19921875" style="1" collapsed="1"/>
-    <col min="12" max="12" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
+    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
+    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
+    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2107,18 +2401,21 @@
         <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="L1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" t="s">
-        <v>159</v>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>248</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2132,16 +2429,16 @@
       <c r="F2" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="s">
-        <v>160</v>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>249</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2158,16 +2455,16 @@
       <c r="G3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="s">
-        <v>161</v>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>250</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2184,16 +2481,16 @@
       <c r="G4" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="1" t="s">
+      <c r="L4" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>162</v>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>251</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2210,16 +2507,16 @@
       <c r="G5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K5" s="1" t="s">
+      <c r="L5" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>163</v>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>252</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2236,16 +2533,16 @@
       <c r="G6" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K6" s="1" t="s">
+      <c r="L6" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A7" t="s">
-        <v>114</v>
-      </c>
-      <c r="B7" t="s">
-        <v>164</v>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>253</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2259,16 +2556,16 @@
       <c r="F7" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K7" s="1" t="s">
+      <c r="L7" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
-        <v>114</v>
-      </c>
-      <c r="B8" t="s">
-        <v>165</v>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>254</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2285,16 +2582,16 @@
       <c r="G8" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K8" s="1" t="s">
+      <c r="L8" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A9" t="s">
-        <v>114</v>
-      </c>
-      <c r="B9" t="s">
-        <v>166</v>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>255</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2311,16 +2608,16 @@
       <c r="G9" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="1" t="s">
+      <c r="L9" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
-        <v>114</v>
-      </c>
-      <c r="B10" t="s">
-        <v>167</v>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>256</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2337,16 +2634,16 @@
       <c r="G10" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K10" s="1" t="s">
+      <c r="L10" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A11" t="s">
-        <v>114</v>
-      </c>
-      <c r="B11" t="s">
-        <v>168</v>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>257</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2363,16 +2660,16 @@
       <c r="G11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K11" s="1" t="s">
+      <c r="L11" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A12" t="s">
-        <v>114</v>
-      </c>
-      <c r="B12" t="s">
-        <v>169</v>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A12" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>258</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2386,16 +2683,16 @@
       <c r="F12" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K12" s="1" t="s">
+      <c r="L12" s="1" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A13" t="s">
-        <v>114</v>
-      </c>
-      <c r="B13" t="s">
-        <v>170</v>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>259</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2412,16 +2709,16 @@
       <c r="G13" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K13" s="1" t="s">
+      <c r="L13" s="1" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>114</v>
-      </c>
-      <c r="B14" t="s">
-        <v>171</v>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>260</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2438,16 +2735,16 @@
       <c r="G14" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K14" s="1" t="s">
+      <c r="L14" s="1" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A15" t="s">
-        <v>114</v>
-      </c>
-      <c r="B15" t="s">
-        <v>172</v>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>261</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2464,16 +2761,16 @@
       <c r="G15" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K15" s="1" t="s">
+      <c r="L15" s="1" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A16" t="s">
-        <v>114</v>
-      </c>
-      <c r="B16" t="s">
-        <v>173</v>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>262</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2490,16 +2787,16 @@
       <c r="G16" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K16" s="1" t="s">
+      <c r="L16" s="1" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A17" t="s">
-        <v>114</v>
-      </c>
-      <c r="B17" t="s">
-        <v>174</v>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>263</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2519,16 +2816,16 @@
       <c r="I17" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K17" s="1" t="s">
+      <c r="L17" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A18" t="s">
-        <v>114</v>
-      </c>
-      <c r="B18" t="s">
-        <v>175</v>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A18" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>264</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2548,16 +2845,16 @@
       <c r="I18" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K18" s="1" t="s">
+      <c r="L18" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A19" t="s">
-        <v>114</v>
-      </c>
-      <c r="B19" t="s">
-        <v>176</v>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>265</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2577,16 +2874,16 @@
       <c r="I19" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K19" s="1" t="s">
+      <c r="L19" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A20" t="s">
-        <v>114</v>
-      </c>
-      <c r="B20" t="s">
-        <v>177</v>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>266</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2600,16 +2897,16 @@
       <c r="F20" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="K20" s="1" t="s">
+      <c r="L20" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A21" t="s">
-        <v>114</v>
-      </c>
-      <c r="B21" t="s">
-        <v>178</v>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A21" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>267</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2629,16 +2926,16 @@
       <c r="J21" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K21" s="1" t="s">
+      <c r="L21" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A22" t="s">
-        <v>114</v>
-      </c>
-      <c r="B22" t="s">
-        <v>179</v>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>268</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2658,16 +2955,16 @@
       <c r="I22" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K22" s="1" t="s">
+      <c r="L22" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A23" t="s">
-        <v>114</v>
-      </c>
-      <c r="B23" t="s">
-        <v>180</v>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>269</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2684,16 +2981,16 @@
       <c r="H23" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K23" s="1" t="s">
+      <c r="L23" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A24" t="s">
-        <v>114</v>
-      </c>
-      <c r="B24" t="s">
-        <v>181</v>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A24" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>270</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -2713,16 +3010,16 @@
       <c r="I24" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K24" s="1" t="s">
+      <c r="L24" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A25" t="s">
-        <v>114</v>
-      </c>
-      <c r="B25" t="s">
-        <v>182</v>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A25" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>271</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -2745,16 +3042,16 @@
       <c r="I25" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K25" s="1" t="s">
+      <c r="L25" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A26" t="s">
-        <v>114</v>
-      </c>
-      <c r="B26" t="s">
-        <v>183</v>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A26" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>272</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -2774,16 +3071,16 @@
       <c r="I26" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K26" s="1" t="s">
+      <c r="L26" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A27" t="s">
-        <v>114</v>
-      </c>
-      <c r="B27" t="s">
-        <v>184</v>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A27" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>273</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -2803,16 +3100,16 @@
       <c r="H27" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K27" s="1" t="s">
+      <c r="L27" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A28" t="s">
-        <v>114</v>
-      </c>
-      <c r="B28" t="s">
-        <v>185</v>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A28" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>274</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -2832,19 +3129,19 @@
       <c r="I28" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K28" s="1" t="s">
+      <c r="L28" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="M28" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A29" t="s">
-        <v>114</v>
-      </c>
-      <c r="B29" t="s">
-        <v>186</v>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A29" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>275</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -2864,16 +3161,16 @@
       <c r="I29" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K29" s="1" t="s">
+      <c r="L29" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A30" t="s">
-        <v>114</v>
-      </c>
-      <c r="B30" t="s">
-        <v>187</v>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A30" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>276</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -2893,16 +3190,16 @@
       <c r="I30" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="L30" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A31" t="s">
-        <v>114</v>
-      </c>
-      <c r="B31" t="s">
-        <v>188</v>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A31" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>277</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -2922,16 +3219,16 @@
       <c r="I31" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="L31" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A32" t="s">
-        <v>114</v>
-      </c>
-      <c r="B32" t="s">
-        <v>189</v>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A32" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>278</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -2945,16 +3242,16 @@
       <c r="F32" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="K32" s="1" t="s">
+      <c r="L32" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A33" t="s">
-        <v>114</v>
-      </c>
-      <c r="B33" t="s">
-        <v>190</v>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A33" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>279</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -2974,16 +3271,16 @@
       <c r="J33" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K33" s="1" t="s">
+      <c r="L33" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A34" t="s">
-        <v>114</v>
-      </c>
-      <c r="B34" t="s">
-        <v>191</v>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A34" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>280</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3003,16 +3300,16 @@
       <c r="I34" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K34" s="1" t="s">
+      <c r="L34" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A35" t="s">
-        <v>114</v>
-      </c>
-      <c r="B35" t="s">
-        <v>192</v>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A35" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>281</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3029,16 +3326,16 @@
       <c r="H35" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K35" s="1" t="s">
+      <c r="L35" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A36" t="s">
-        <v>114</v>
-      </c>
-      <c r="B36" t="s">
-        <v>193</v>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A36" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>282</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3058,16 +3355,16 @@
       <c r="I36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K36" s="1" t="s">
+      <c r="L36" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A37" t="s">
-        <v>114</v>
-      </c>
-      <c r="B37" t="s">
-        <v>194</v>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A37" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>283</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3090,16 +3387,16 @@
       <c r="I37" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K37" s="1" t="s">
+      <c r="L37" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A38" t="s">
-        <v>114</v>
-      </c>
-      <c r="B38" t="s">
-        <v>195</v>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A38" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>284</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3119,16 +3416,16 @@
       <c r="I38" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K38" s="1" t="s">
+      <c r="L38" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A39" t="s">
-        <v>114</v>
-      </c>
-      <c r="B39" t="s">
-        <v>196</v>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A39" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>285</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3148,16 +3445,16 @@
       <c r="H39" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K39" s="1" t="s">
+      <c r="L39" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A40" t="s">
-        <v>114</v>
-      </c>
-      <c r="B40" t="s">
-        <v>197</v>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A40" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>286</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3177,19 +3474,19 @@
       <c r="I40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K40" s="1" t="s">
+      <c r="L40" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="M40" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A41" t="s">
-        <v>114</v>
-      </c>
-      <c r="B41" t="s">
-        <v>198</v>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A41" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>287</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3209,16 +3506,16 @@
       <c r="I41" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="K41" s="1" t="s">
+      <c r="L41" s="1" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A42" t="s">
-        <v>114</v>
-      </c>
-      <c r="B42" t="s">
-        <v>199</v>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A42" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>288</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3238,16 +3535,16 @@
       <c r="I42" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K42" s="1" t="s">
+      <c r="L42" s="1" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B43" t="s">
-        <v>200</v>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A43" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>289</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3267,16 +3564,16 @@
       <c r="I43" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="K43" s="1" t="s">
+      <c r="L43" s="1" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A44" t="s">
-        <v>114</v>
-      </c>
-      <c r="B44" t="s">
-        <v>201</v>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A44" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>290</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3290,16 +3587,16 @@
       <c r="F44" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K44" s="1" t="s">
+      <c r="L44" s="1" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A45" t="s">
-        <v>114</v>
-      </c>
-      <c r="B45" t="s">
-        <v>202</v>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A45" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>291</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3319,16 +3616,16 @@
       <c r="J45" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K45" s="1" t="s">
+      <c r="L45" s="1" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A46" t="s">
-        <v>114</v>
-      </c>
-      <c r="B46" t="s">
-        <v>203</v>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A46" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>292</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3348,16 +3645,16 @@
       <c r="I46" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="K46" s="1" t="s">
+      <c r="L46" s="1" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A47" t="s">
-        <v>114</v>
-      </c>
-      <c r="B47" t="s">
-        <v>204</v>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A47" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B47" s="1" t="s">
+        <v>293</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3374,16 +3671,16 @@
       <c r="H47" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K47" s="1" t="s">
+      <c r="L47" s="1" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A48" t="s">
-        <v>114</v>
-      </c>
-      <c r="B48" t="s">
-        <v>205</v>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A48" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B48" s="1" t="s">
+        <v>294</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3403,16 +3700,16 @@
       <c r="I48" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="K48" s="1" t="s">
+      <c r="L48" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A49" t="s">
-        <v>114</v>
-      </c>
-      <c r="B49" t="s">
-        <v>206</v>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A49" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B49" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3435,16 +3732,16 @@
       <c r="I49" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="K49" s="1" t="s">
+      <c r="L49" s="1" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A50" t="s">
-        <v>114</v>
-      </c>
-      <c r="B50" t="s">
-        <v>207</v>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A50" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B50" s="1" t="s">
+        <v>296</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3464,16 +3761,16 @@
       <c r="I50" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="K50" s="1" t="s">
+      <c r="L50" s="1" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A51" t="s">
-        <v>114</v>
-      </c>
-      <c r="B51" t="s">
-        <v>208</v>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A51" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B51" s="1" t="s">
+        <v>297</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3493,16 +3790,16 @@
       <c r="H51" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K51" s="1" t="s">
+      <c r="L51" s="1" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A52" t="s">
-        <v>114</v>
-      </c>
-      <c r="B52" t="s">
-        <v>209</v>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A52" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B52" s="1" t="s">
+        <v>298</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3522,19 +3819,19 @@
       <c r="I52" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="K52" s="1" t="s">
+      <c r="L52" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="M52" s="1" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A53" t="s">
-        <v>114</v>
-      </c>
-      <c r="B53" t="s">
-        <v>210</v>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A53" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>299</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3548,19 +3845,13 @@
       <c r="F53" s="1" t="s">
         <v>115</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="M53" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A54" t="s">
-        <v>114</v>
-      </c>
-      <c r="B54" t="s">
-        <v>211</v>
-      </c>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C54" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>15</v>
@@ -3574,13 +3865,11 @@
       <c r="G54" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="M54" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A55"/>
-      <c r="B55"/>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C55" s="1" t="s">
         <v>32</v>
       </c>
@@ -3600,12 +3889,12 @@
         <v>22</v>
       </c>
     </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A56" t="s">
-        <v>114</v>
-      </c>
-      <c r="B56" t="s">
-        <v>212</v>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A56" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>300</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3619,19 +3908,13 @@
       <c r="F56" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="M56" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A57" t="s">
-        <v>114</v>
-      </c>
-      <c r="B57" t="s">
-        <v>213</v>
-      </c>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C57" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
@@ -3645,13 +3928,11 @@
       <c r="G57" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L57" s="1" t="s">
+      <c r="M57" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A58"/>
-      <c r="B58"/>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C58" s="1" t="s">
         <v>32</v>
       </c>
@@ -3671,12 +3952,12 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A59" t="s">
-        <v>114</v>
-      </c>
-      <c r="B59" t="s">
-        <v>214</v>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A59" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B59" s="1" t="s">
+        <v>301</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3690,19 +3971,13 @@
       <c r="F59" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="M59" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A60" t="s">
-        <v>114</v>
-      </c>
-      <c r="B60" t="s">
-        <v>215</v>
-      </c>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C60" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>15</v>
@@ -3716,13 +3991,11 @@
       <c r="G60" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="M60" s="1" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.45">
-      <c r="A61"/>
-      <c r="B61"/>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.45">
       <c r="C61" s="1" t="s">
         <v>32</v>
       </c>
@@ -3740,6 +4013,84 @@
       </c>
       <c r="I61" s="1" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A62" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>302</v>
+      </c>
+      <c r="C62" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D62" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E62" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F62" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="I62" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K62" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A63" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>303</v>
+      </c>
+      <c r="C63" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D63" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E63" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F63" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I63" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K63" s="1" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A64" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B64" t="s" s="1">
+        <v>304</v>
+      </c>
+      <c r="C64" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D64" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E64" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="F64" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I64" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="K64" s="1" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3757,14 +4108,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
-    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
+    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
+    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -3794,11 +4145,11 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" t="s">
-        <v>149</v>
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>306</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -3817,11 +4168,11 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="s">
-        <v>150</v>
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>307</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -3840,11 +4191,11 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="s">
-        <v>151</v>
+      <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>308</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -3863,11 +4214,11 @@
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>152</v>
+      <c r="A5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>309</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -3886,11 +4237,11 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>153</v>
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>310</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -3909,8 +4260,6 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A7"/>
-      <c r="B7"/>
       <c r="C7" s="1" t="s">
         <v>32</v>
       </c>
@@ -3925,8 +4274,6 @@
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A8"/>
-      <c r="B8"/>
       <c r="C8" s="1" t="s">
         <v>32</v>
       </c>
@@ -3941,8 +4288,6 @@
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
-      <c r="A9"/>
-      <c r="B9"/>
       <c r="C9" s="1" t="s">
         <v>32</v>
       </c>
@@ -3966,14 +4311,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
-    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
+    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
+    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4000,11 +4345,11 @@
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" t="s">
-        <v>154</v>
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>311</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4023,11 +4368,11 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A3" t="s">
-        <v>114</v>
-      </c>
-      <c r="B3" t="s">
-        <v>155</v>
+      <c r="A3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>312</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4046,11 +4391,11 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A4" t="s">
-        <v>114</v>
-      </c>
-      <c r="B4" t="s">
-        <v>156</v>
+      <c r="A4" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>313</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4069,11 +4414,11 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A5" t="s">
-        <v>114</v>
-      </c>
-      <c r="B5" t="s">
-        <v>157</v>
+      <c r="A5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>314</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4092,11 +4437,11 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.45">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" t="s">
-        <v>158</v>
+      <c r="A6" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>315</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4124,12 +4469,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
-    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
+    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
+    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
+    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
+    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
+    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
+    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4153,11 +4498,11 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A2" t="s">
-        <v>114</v>
-      </c>
-      <c r="B2" t="s">
-        <v>148</v>
+      <c r="A2" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>305</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4173,8 +4518,6 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.45">
-      <c r="A3"/>
-      <c r="B3"/>
       <c r="C3" s="1" t="s">
         <v>32</v>
       </c>

--- a/KatalonData/RADTestData/ChangePaymentMethod.xlsx
+++ b/KatalonData/RADTestData/ChangePaymentMethod.xlsx
@@ -3,14 +3,14 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F1A9B65-B8E4-413D-A306-37F2DD2B058C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504C78B4-45EB-4530-B854-45E59B123856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="45972" yWindow="2952" windowWidth="30936" windowHeight="16776" activeTab="3" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
+    <workbookView xWindow="3877" yWindow="3143" windowWidth="21601" windowHeight="11325" activeTab="4" xr2:uid="{D99FAB39-5CE6-4AA4-B9C6-99B1EFA0654E}"/>
   </bookViews>
   <sheets>
     <sheet name="Estimated" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="224">
   <si>
     <t>Result</t>
   </si>
@@ -395,309 +395,12 @@
     <t>2026</t>
   </si>
   <si>
-    <t>Sat May 23 22:32:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:33:47 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:34:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:35:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:36:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:37:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:38:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:54:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:55:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:56:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:57:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:57:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:58:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 22:59:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:00:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:01:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:01:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:02:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:03:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:04:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:05:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:06:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:06:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:07:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:08:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:10:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:11:20 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:12:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:13:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:14:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sat May 23 23:16:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:42:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:44:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:45:30 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:46:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:48:13 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:49:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:50:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:52:34 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:54:11 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:55:40 EDT 2026</t>
-  </si>
-  <si>
-    <t>Sun May 24 04:57:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:41:26 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:41:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:42:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:42:54 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:43:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:43:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:44:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:44:35 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:44:58 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:45:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:45:46 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:46:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:46:38 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:47:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:47:25 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:47:52 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:48:16 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:48:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:49:04 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:49:28 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:49:53 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:50:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:50:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:51:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:51:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:51:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:52:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:52:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:53:07 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:53:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:53:56 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:54:19 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:54:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:55:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:55:33 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:56:03 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:56:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:56:55 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:57:24 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:57:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:58:17 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:58:45 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:59:09 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 15:59:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:00:22 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:00:49 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:01:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:01:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:02:12 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:02:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:02:59 EDT 2026</t>
-  </si>
-  <si>
-    <t>Mon May 25 16:04:37 EDT 2026</t>
-  </si>
-  <si>
     <t>MFInsNum</t>
   </si>
   <si>
     <t>Motor Fuel Floor Tax</t>
   </si>
   <si>
-    <t>Fri Jul 10 16:05:14 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 16:05:43 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 16:06:08 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 16:06:31 EDT 2026</t>
-  </si>
-  <si>
-    <t>Fri Jul 10 16:06:55 EDT 2026</t>
-  </si>
-  <si>
     <t>Fri Jul 10 22:58:30 EDT 2026</t>
   </si>
   <si>
@@ -993,13 +696,33 @@
   </si>
   <si>
     <t>Fri Jul 10 23:40:02 EDT 2026</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 16:25:06 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 16:25:35 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 16:26:00 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:46:53 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:47:26 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sun Aug 02 21:47:56 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1372,17 +1095,17 @@
   <dimension ref="A1:J8"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="44.53125" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="35.53125" collapsed="true"/>
-    <col min="6" max="6" customWidth="true" style="1" width="15.265625" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.265625" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="19.53125" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="18.46484375" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="44.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="35.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="15.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="7" max="7" width="17.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="19.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="18.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1422,7 +1145,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>217</v>
+        <v>118</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1451,7 +1174,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>218</v>
+        <v>119</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1480,7 +1203,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>219</v>
+        <v>120</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1512,7 +1235,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>220</v>
+        <v>121</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1544,7 +1267,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>221</v>
+        <v>122</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1576,7 +1299,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>222</v>
+        <v>123</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1608,7 +1331,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>223</v>
+        <v>124</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1641,16 +1364,16 @@
   <dimension ref="A1:J21"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" customWidth="true" style="1" width="14.53125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.59765625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="52.0" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="9" style="1" width="9.19921875" collapsed="true"/>
-    <col min="10" max="10" customWidth="true" style="1" width="43.33203125" collapsed="true"/>
-    <col min="11" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="14.53125" style="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.59765625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="52" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="9" width="9.19921875" style="1" collapsed="1"/>
+    <col min="10" max="10" width="43.33203125" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.45">
@@ -1690,7 +1413,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>224</v>
+        <v>125</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -1713,7 +1436,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>225</v>
+        <v>126</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -1736,7 +1459,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>226</v>
+        <v>127</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -1759,7 +1482,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>227</v>
+        <v>128</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -1785,7 +1508,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>228</v>
+        <v>129</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -1811,7 +1534,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>229</v>
+        <v>130</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -1834,7 +1557,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>230</v>
+        <v>131</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -1857,7 +1580,7 @@
         <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>231</v>
+        <v>132</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -1880,7 +1603,7 @@
         <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>232</v>
+        <v>133</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -1903,7 +1626,7 @@
         <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>233</v>
+        <v>134</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -1926,7 +1649,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>234</v>
+        <v>135</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -1949,7 +1672,7 @@
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>235</v>
+        <v>136</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -1972,7 +1695,7 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>236</v>
+        <v>137</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -1995,7 +1718,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>237</v>
+        <v>138</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2015,7 +1738,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>238</v>
+        <v>139</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2041,7 +1764,7 @@
         <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>239</v>
+        <v>140</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2064,7 +1787,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>240</v>
+        <v>141</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2104,7 +1827,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>241</v>
+        <v>142</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2149,15 +1872,15 @@
   <dimension ref="A1:I7"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.265625" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="19.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="24.46484375" collapsed="true"/>
-    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="27.0" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="17.0" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.265625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="19.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="24.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="27" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="8" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.45">
@@ -2194,7 +1917,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>242</v>
+        <v>143</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2220,7 +1943,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>243</v>
+        <v>144</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2243,7 +1966,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>244</v>
+        <v>145</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2269,7 +1992,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>245</v>
+        <v>146</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2295,7 +2018,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>246</v>
+        <v>147</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2321,7 +2044,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>247</v>
+        <v>148</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2356,17 +2079,17 @@
   <dimension ref="A1:M64"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.19921875" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="12.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="31.73046875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="41.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="10" customWidth="true" style="1" width="19.796875" collapsed="true"/>
-    <col min="11" max="11" customWidth="true" style="1" width="19.796875"/>
-    <col min="12" max="12" style="1" width="9.19921875" collapsed="true"/>
-    <col min="13" max="13" customWidth="true" style="1" width="43.19921875" collapsed="true"/>
-    <col min="14" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.19921875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="12.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="31.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="41.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="10" width="19.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="11" max="11" width="19.796875" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9.19921875" style="1" collapsed="1"/>
+    <col min="13" max="13" width="43.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="14" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.45">
@@ -2401,7 +2124,7 @@
         <v>108</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>210</v>
+        <v>116</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>43</v>
@@ -2415,7 +2138,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>248</v>
+        <v>149</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -2438,7 +2161,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>249</v>
+        <v>150</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -2464,7 +2187,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>250</v>
+        <v>151</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -2490,7 +2213,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>251</v>
+        <v>152</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -2516,7 +2239,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>252</v>
+        <v>153</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -2542,7 +2265,7 @@
         <v>114</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>253</v>
+        <v>154</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>29</v>
@@ -2565,7 +2288,7 @@
         <v>114</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>254</v>
+        <v>155</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>29</v>
@@ -2591,7 +2314,7 @@
         <v>114</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>255</v>
+        <v>156</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>29</v>
@@ -2617,7 +2340,7 @@
         <v>114</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>256</v>
+        <v>157</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>29</v>
@@ -2643,7 +2366,7 @@
         <v>114</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>257</v>
+        <v>158</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>29</v>
@@ -2669,7 +2392,7 @@
         <v>114</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>258</v>
+        <v>159</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>29</v>
@@ -2692,7 +2415,7 @@
         <v>114</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>259</v>
+        <v>160</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>29</v>
@@ -2718,7 +2441,7 @@
         <v>114</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>260</v>
+        <v>161</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>29</v>
@@ -2744,7 +2467,7 @@
         <v>114</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>261</v>
+        <v>162</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>29</v>
@@ -2770,7 +2493,7 @@
         <v>114</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>262</v>
+        <v>163</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>29</v>
@@ -2796,7 +2519,7 @@
         <v>114</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>263</v>
+        <v>164</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>29</v>
@@ -2825,7 +2548,7 @@
         <v>114</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>264</v>
+        <v>165</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>29</v>
@@ -2854,7 +2577,7 @@
         <v>114</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>265</v>
+        <v>166</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>29</v>
@@ -2883,7 +2606,7 @@
         <v>114</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>266</v>
+        <v>167</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>29</v>
@@ -2906,7 +2629,7 @@
         <v>114</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>267</v>
+        <v>168</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>29</v>
@@ -2935,7 +2658,7 @@
         <v>114</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>268</v>
+        <v>169</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>29</v>
@@ -2964,7 +2687,7 @@
         <v>114</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>269</v>
+        <v>170</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>29</v>
@@ -2990,7 +2713,7 @@
         <v>114</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>270</v>
+        <v>171</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>29</v>
@@ -3019,7 +2742,7 @@
         <v>114</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>271</v>
+        <v>172</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>29</v>
@@ -3051,7 +2774,7 @@
         <v>114</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>272</v>
+        <v>173</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>29</v>
@@ -3080,7 +2803,7 @@
         <v>114</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>273</v>
+        <v>174</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>29</v>
@@ -3109,7 +2832,7 @@
         <v>114</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>274</v>
+        <v>175</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>29</v>
@@ -3141,7 +2864,7 @@
         <v>114</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>275</v>
+        <v>176</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>29</v>
@@ -3170,7 +2893,7 @@
         <v>114</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>276</v>
+        <v>177</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>29</v>
@@ -3199,7 +2922,7 @@
         <v>114</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>277</v>
+        <v>178</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>29</v>
@@ -3228,7 +2951,7 @@
         <v>114</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>278</v>
+        <v>179</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>29</v>
@@ -3251,7 +2974,7 @@
         <v>114</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>279</v>
+        <v>180</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>29</v>
@@ -3280,7 +3003,7 @@
         <v>114</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>280</v>
+        <v>181</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>29</v>
@@ -3309,7 +3032,7 @@
         <v>114</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>281</v>
+        <v>182</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>29</v>
@@ -3335,7 +3058,7 @@
         <v>114</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>282</v>
+        <v>183</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>29</v>
@@ -3364,7 +3087,7 @@
         <v>114</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>283</v>
+        <v>184</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>29</v>
@@ -3396,7 +3119,7 @@
         <v>114</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>284</v>
+        <v>185</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>29</v>
@@ -3425,7 +3148,7 @@
         <v>114</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>285</v>
+        <v>186</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>29</v>
@@ -3454,7 +3177,7 @@
         <v>114</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>286</v>
+        <v>187</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>29</v>
@@ -3486,7 +3209,7 @@
         <v>114</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>287</v>
+        <v>188</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>29</v>
@@ -3515,7 +3238,7 @@
         <v>114</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>288</v>
+        <v>189</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>29</v>
@@ -3544,7 +3267,7 @@
         <v>114</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>289</v>
+        <v>190</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>29</v>
@@ -3573,7 +3296,7 @@
         <v>114</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>290</v>
+        <v>191</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>29</v>
@@ -3596,7 +3319,7 @@
         <v>114</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>291</v>
+        <v>192</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>29</v>
@@ -3625,7 +3348,7 @@
         <v>114</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>292</v>
+        <v>193</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>29</v>
@@ -3654,7 +3377,7 @@
         <v>114</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>293</v>
+        <v>194</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>29</v>
@@ -3680,7 +3403,7 @@
         <v>114</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>294</v>
+        <v>195</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>29</v>
@@ -3709,7 +3432,7 @@
         <v>114</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>295</v>
+        <v>196</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>29</v>
@@ -3741,7 +3464,7 @@
         <v>114</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>296</v>
+        <v>197</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>29</v>
@@ -3770,7 +3493,7 @@
         <v>114</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>297</v>
+        <v>198</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>29</v>
@@ -3799,7 +3522,7 @@
         <v>114</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>298</v>
+        <v>199</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>29</v>
@@ -3831,7 +3554,7 @@
         <v>114</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>299</v>
+        <v>200</v>
       </c>
       <c r="C53" s="1" t="s">
         <v>29</v>
@@ -3850,8 +3573,14 @@
       </c>
     </row>
     <row r="54" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A54" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B54" s="1" t="s">
+        <v>218</v>
+      </c>
       <c r="C54" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D54" s="1" t="s">
         <v>15</v>
@@ -3894,7 +3623,7 @@
         <v>114</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>300</v>
+        <v>201</v>
       </c>
       <c r="C56" s="1" t="s">
         <v>29</v>
@@ -3913,8 +3642,14 @@
       </c>
     </row>
     <row r="57" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A57" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>219</v>
+      </c>
       <c r="C57" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D57" s="1" t="s">
         <v>15</v>
@@ -3957,7 +3692,7 @@
         <v>114</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>301</v>
+        <v>202</v>
       </c>
       <c r="C59" s="1" t="s">
         <v>29</v>
@@ -3976,8 +3711,14 @@
       </c>
     </row>
     <row r="60" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A60" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="B60" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="C60" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D60" s="1" t="s">
         <v>15</v>
@@ -4020,7 +3761,7 @@
         <v>114</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>302</v>
+        <v>203</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>29</v>
@@ -4029,7 +3770,7 @@
         <v>15</v>
       </c>
       <c r="E62" s="1" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>115</v>
@@ -4046,7 +3787,7 @@
         <v>114</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>303</v>
+        <v>204</v>
       </c>
       <c r="C63" s="1" t="s">
         <v>29</v>
@@ -4055,7 +3796,7 @@
         <v>15</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="F63" s="1" t="s">
         <v>109</v>
@@ -4071,8 +3812,8 @@
       <c r="A64" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B64" t="s" s="1">
-        <v>304</v>
+      <c r="B64" s="1" t="s">
+        <v>205</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>29</v>
@@ -4081,7 +3822,7 @@
         <v>15</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>211</v>
+        <v>117</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>33</v>
@@ -4108,14 +3849,14 @@
   <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="27.53125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.19921875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="7" style="1" width="9.19921875" collapsed="true"/>
-    <col min="8" max="8" customWidth="true" style="1" width="23.46484375" collapsed="true"/>
-    <col min="9" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="27.53125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="7" width="9.19921875" style="1" collapsed="1"/>
+    <col min="8" max="8" width="23.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="9" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.45">
@@ -4149,7 +3890,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>306</v>
+        <v>207</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4172,7 +3913,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>307</v>
+        <v>208</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4195,7 +3936,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>308</v>
+        <v>209</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4218,7 +3959,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>309</v>
+        <v>210</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4241,7 +3982,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>310</v>
+        <v>211</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4260,8 +4001,14 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>221</v>
+      </c>
       <c r="C7" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>15</v>
@@ -4270,12 +4017,18 @@
         <v>35</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>222</v>
+      </c>
       <c r="C8" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>15</v>
@@ -4284,12 +4037,18 @@
         <v>35</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>33</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A9" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="B9" t="s">
+        <v>223</v>
+      </c>
       <c r="C9" s="1" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>15</v>
@@ -4298,7 +4057,7 @@
         <v>35</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4311,14 +4070,14 @@
   <dimension ref="A1:G6"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.265625" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="6" style="1" width="9.19921875" collapsed="true"/>
-    <col min="7" max="7" customWidth="true" style="1" width="14.19921875" collapsed="true"/>
-    <col min="8" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="6" width="9.19921875" style="1" collapsed="1"/>
+    <col min="7" max="7" width="14.19921875" style="1" customWidth="1" collapsed="1"/>
+    <col min="8" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.45">
@@ -4349,7 +4108,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>311</v>
+        <v>212</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
@@ -4372,7 +4131,7 @@
         <v>114</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>312</v>
+        <v>213</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>29</v>
@@ -4395,7 +4154,7 @@
         <v>114</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>313</v>
+        <v>214</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>29</v>
@@ -4418,7 +4177,7 @@
         <v>114</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>314</v>
+        <v>215</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>29</v>
@@ -4441,7 +4200,7 @@
         <v>114</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>315</v>
+        <v>216</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>29</v>
@@ -4469,12 +4228,12 @@
   <dimension ref="A1:F3"/>
   <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" style="1" width="9.19921875" collapsed="true"/>
-    <col min="2" max="2" customWidth="true" style="1" width="32.46484375" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="16.73046875" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.796875" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="46.265625" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.19921875" collapsed="true"/>
+    <col min="1" max="1" width="9.19921875" style="1" collapsed="1"/>
+    <col min="2" max="2" width="32.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="16.73046875" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="46.265625" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.45">
@@ -4502,7 +4261,7 @@
         <v>114</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>305</v>
+        <v>206</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>29</v>
